--- a/Test Hardware/980HX-8880F5-KBG-A10/Final/assign.xlsx
+++ b/Test Hardware/980HX-8880F5-KBG-A10/Final/assign.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\iTest\homeoffice\Test Hardware\980HX-8880F5-KBG-A10\Final\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D64C2D2B-3C67-4C26-9EA0-69F81C13DD1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7984A290-B6DF-4BCB-97E1-5F6E3B2B8E99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="615" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PS9G" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="704">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="702">
   <si>
     <t>D30206</t>
   </si>
@@ -1152,9 +1152,6 @@
     <t>D12714</t>
   </si>
   <si>
-    <t>D12814</t>
-  </si>
-  <si>
     <t>D12613</t>
   </si>
   <si>
@@ -1176,9 +1173,6 @@
     <t>D12712</t>
   </si>
   <si>
-    <t>D12812</t>
-  </si>
-  <si>
     <t>D12611</t>
   </si>
   <si>
@@ -1257,9 +1251,6 @@
     <t>D12705</t>
   </si>
   <si>
-    <t>D12805</t>
-  </si>
-  <si>
     <t>D12505</t>
   </si>
   <si>
@@ -1281,9 +1272,6 @@
     <t>D12703</t>
   </si>
   <si>
-    <t>D12803</t>
-  </si>
-  <si>
     <t>D12503</t>
   </si>
   <si>
@@ -2149,6 +2137,12 @@
   </si>
   <si>
     <t>S1_Rly_001</t>
+  </si>
+  <si>
+    <t>D12308</t>
+  </si>
+  <si>
+    <t>D12306</t>
   </si>
 </sst>
 </file>
@@ -2467,14 +2461,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B96"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>96</v>
       </c>
@@ -2482,7 +2476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>97</v>
       </c>
@@ -2490,7 +2484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>98</v>
       </c>
@@ -2498,7 +2492,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>99</v>
       </c>
@@ -2506,7 +2500,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>100</v>
       </c>
@@ -2514,7 +2508,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>101</v>
       </c>
@@ -2522,7 +2516,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>102</v>
       </c>
@@ -2530,7 +2524,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>103</v>
       </c>
@@ -2538,7 +2532,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>104</v>
       </c>
@@ -2546,7 +2540,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>105</v>
       </c>
@@ -2554,7 +2548,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>106</v>
       </c>
@@ -2562,7 +2556,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>107</v>
       </c>
@@ -2570,7 +2564,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>108</v>
       </c>
@@ -2578,7 +2572,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>109</v>
       </c>
@@ -2586,7 +2580,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>110</v>
       </c>
@@ -2594,7 +2588,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>111</v>
       </c>
@@ -2602,7 +2596,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>112</v>
       </c>
@@ -2610,7 +2604,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>113</v>
       </c>
@@ -2618,7 +2612,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>114</v>
       </c>
@@ -2626,7 +2620,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>115</v>
       </c>
@@ -2634,7 +2628,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>116</v>
       </c>
@@ -2642,7 +2636,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>117</v>
       </c>
@@ -2650,7 +2644,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>118</v>
       </c>
@@ -2658,7 +2652,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>119</v>
       </c>
@@ -2666,7 +2660,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>120</v>
       </c>
@@ -2674,7 +2668,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>121</v>
       </c>
@@ -2682,7 +2676,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>122</v>
       </c>
@@ -2690,7 +2684,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>123</v>
       </c>
@@ -2698,7 +2692,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>124</v>
       </c>
@@ -2706,7 +2700,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>125</v>
       </c>
@@ -2714,7 +2708,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>126</v>
       </c>
@@ -2722,7 +2716,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>127</v>
       </c>
@@ -2730,7 +2724,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>128</v>
       </c>
@@ -2738,7 +2732,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>129</v>
       </c>
@@ -2746,7 +2740,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>130</v>
       </c>
@@ -2754,7 +2748,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>131</v>
       </c>
@@ -2762,7 +2756,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>132</v>
       </c>
@@ -2770,7 +2764,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>133</v>
       </c>
@@ -2778,7 +2772,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>134</v>
       </c>
@@ -2786,7 +2780,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>135</v>
       </c>
@@ -2794,7 +2788,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>136</v>
       </c>
@@ -2802,7 +2796,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>137</v>
       </c>
@@ -2810,7 +2804,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>138</v>
       </c>
@@ -2818,7 +2812,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>139</v>
       </c>
@@ -2826,7 +2820,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>140</v>
       </c>
@@ -2834,7 +2828,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>141</v>
       </c>
@@ -2842,7 +2836,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>142</v>
       </c>
@@ -2850,7 +2844,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>143</v>
       </c>
@@ -2858,7 +2852,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>144</v>
       </c>
@@ -2866,7 +2860,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>145</v>
       </c>
@@ -2874,7 +2868,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>146</v>
       </c>
@@ -2882,7 +2876,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>147</v>
       </c>
@@ -2890,7 +2884,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>148</v>
       </c>
@@ -2898,7 +2892,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>149</v>
       </c>
@@ -2906,7 +2900,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>150</v>
       </c>
@@ -2914,7 +2908,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>151</v>
       </c>
@@ -2922,7 +2916,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>152</v>
       </c>
@@ -2930,7 +2924,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>153</v>
       </c>
@@ -2938,7 +2932,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>154</v>
       </c>
@@ -2946,7 +2940,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>155</v>
       </c>
@@ -2954,7 +2948,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>156</v>
       </c>
@@ -2962,7 +2956,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>157</v>
       </c>
@@ -2970,7 +2964,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>158</v>
       </c>
@@ -2978,7 +2972,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>159</v>
       </c>
@@ -2986,7 +2980,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>160</v>
       </c>
@@ -2994,7 +2988,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>161</v>
       </c>
@@ -3002,7 +2996,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>162</v>
       </c>
@@ -3010,7 +3004,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>163</v>
       </c>
@@ -3018,7 +3012,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>164</v>
       </c>
@@ -3026,7 +3020,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>165</v>
       </c>
@@ -3034,7 +3028,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>166</v>
       </c>
@@ -3042,7 +3036,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>167</v>
       </c>
@@ -3050,7 +3044,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>168</v>
       </c>
@@ -3058,7 +3052,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>169</v>
       </c>
@@ -3066,7 +3060,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>170</v>
       </c>
@@ -3074,7 +3068,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>171</v>
       </c>
@@ -3082,7 +3076,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>172</v>
       </c>
@@ -3090,7 +3084,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>173</v>
       </c>
@@ -3098,7 +3092,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>174</v>
       </c>
@@ -3106,7 +3100,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>175</v>
       </c>
@@ -3114,7 +3108,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>176</v>
       </c>
@@ -3122,7 +3116,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>177</v>
       </c>
@@ -3130,7 +3124,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>178</v>
       </c>
@@ -3138,7 +3132,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>179</v>
       </c>
@@ -3146,7 +3140,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>180</v>
       </c>
@@ -3154,7 +3148,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>181</v>
       </c>
@@ -3162,7 +3156,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>182</v>
       </c>
@@ -3170,7 +3164,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>183</v>
       </c>
@@ -3178,7 +3172,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>184</v>
       </c>
@@ -3186,7 +3180,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>185</v>
       </c>
@@ -3194,7 +3188,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>186</v>
       </c>
@@ -3202,7 +3196,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>187</v>
       </c>
@@ -3210,7 +3204,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>188</v>
       </c>
@@ -3218,7 +3212,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>189</v>
       </c>
@@ -3226,7 +3220,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>190</v>
       </c>
@@ -3234,7 +3228,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>191</v>
       </c>
@@ -3250,139 +3244,139 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C205966-2416-4BB7-B967-6FB23C9784ED}">
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>420</v>
+      </c>
+      <c r="B1" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>421</v>
+      </c>
+      <c r="B2" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>422</v>
+      </c>
+      <c r="B3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>423</v>
+      </c>
+      <c r="B4" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>424</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B5" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>425</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B6" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>426</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B7" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>427</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B8" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>428</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B9" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>429</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B10" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>430</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B11" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>431</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B12" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>432</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B13" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>433</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B14" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>434</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B15" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>435</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B16" t="s">
         <v>451</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>436</v>
-      </c>
-      <c r="B13" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>437</v>
-      </c>
-      <c r="B14" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>438</v>
-      </c>
-      <c r="B15" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>439</v>
-      </c>
-      <c r="B16" t="s">
-        <v>455</v>
       </c>
     </row>
   </sheetData>
@@ -3393,1003 +3387,1003 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C00786B4-E47F-4EFF-A3A7-B38487F70882}">
   <dimension ref="A1:B124"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>576</v>
+      </c>
+      <c r="B1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>577</v>
+      </c>
+      <c r="B2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>578</v>
+      </c>
+      <c r="B3" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>579</v>
+      </c>
+      <c r="B4" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>580</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B5" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>581</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B6" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>582</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B7" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>583</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B8" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>584</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B9" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>585</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B10" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>586</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B11" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>587</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B12" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>588</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B13" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>589</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B14" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>590</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B15" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>591</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B16" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>592</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B17" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>593</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B18" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
         <v>594</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B19" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
         <v>595</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B20" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
         <v>596</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B21" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>597</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B22" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>598</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B23" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
         <v>599</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B24" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
         <v>600</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B25" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>601</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B26" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>602</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B27" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
         <v>603</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B28" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>604</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B29" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
         <v>605</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B30" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>606</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B31" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>607</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B32" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>608</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B33" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
         <v>609</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B34" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
         <v>610</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B35" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
         <v>611</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B36" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
         <v>612</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B37" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
         <v>613</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B38" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
         <v>614</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B39" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
         <v>615</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B40" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
         <v>616</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B41" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
         <v>617</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B42" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
         <v>618</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B43" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
         <v>619</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B44" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
         <v>620</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B45" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
         <v>621</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B46" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
         <v>622</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B47" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
         <v>623</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B48" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
         <v>624</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B49" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
         <v>625</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B50" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
         <v>626</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B51" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
         <v>627</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B52" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
         <v>628</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B53" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
         <v>629</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B54" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
         <v>630</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B55" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
         <v>631</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B56" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
         <v>632</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B57" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
         <v>633</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B58" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
         <v>634</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B59" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
         <v>635</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B60" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
         <v>636</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B61" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
         <v>637</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B62" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
         <v>638</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B63" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
         <v>639</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B64" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
         <v>640</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B65" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
         <v>641</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B66" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
         <v>642</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B67" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
         <v>643</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B68" t="s">
         <v>519</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
         <v>644</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B69" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
         <v>645</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B70" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
         <v>646</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B71" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
         <v>647</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B72" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
         <v>648</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B73" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
         <v>649</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B74" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
         <v>650</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B75" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
         <v>651</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B76" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
         <v>652</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B77" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
         <v>653</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B78" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>654</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B79" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
         <v>655</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B80" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
         <v>656</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B81" t="s">
         <v>532</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
         <v>657</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B82" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
         <v>658</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B83" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
         <v>659</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B84" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
         <v>660</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B85" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
         <v>661</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B86" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
         <v>662</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B87" t="s">
         <v>538</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
         <v>663</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B88" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
         <v>664</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B89" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
         <v>665</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B90" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
         <v>666</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B91" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
         <v>667</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B92" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
         <v>668</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B93" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
         <v>669</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B94" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
         <v>670</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B95" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
         <v>671</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B96" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
         <v>672</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B97" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
         <v>673</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B98" t="s">
         <v>549</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
         <v>674</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B99" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
         <v>675</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B100" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
         <v>676</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B101" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
         <v>677</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B102" t="s">
         <v>553</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
         <v>678</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B103" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
         <v>679</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B104" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
         <v>680</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B105" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
         <v>681</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B106" t="s">
         <v>557</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
         <v>682</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B107" t="s">
         <v>558</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
         <v>683</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B108" t="s">
         <v>559</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
         <v>684</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B109" t="s">
         <v>560</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
         <v>685</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B110" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
         <v>686</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B111" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
         <v>687</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B112" t="s">
         <v>563</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
         <v>688</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B113" t="s">
         <v>564</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
         <v>689</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B114" t="s">
         <v>565</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
         <v>690</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B115" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
         <v>691</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B116" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
         <v>692</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B117" t="s">
         <v>568</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
         <v>693</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B118" t="s">
         <v>569</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
         <v>694</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B119" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
         <v>695</v>
       </c>
-      <c r="B116" t="s">
+      <c r="B120" t="s">
         <v>571</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
         <v>696</v>
       </c>
-      <c r="B117" t="s">
+      <c r="B121" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
         <v>697</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B122" t="s">
         <v>573</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
         <v>698</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B123" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
         <v>699</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B124" t="s">
         <v>575</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
-        <v>700</v>
-      </c>
-      <c r="B121" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
-        <v>701</v>
-      </c>
-      <c r="B122" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
-        <v>702</v>
-      </c>
-      <c r="B123" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
-        <v>703</v>
-      </c>
-      <c r="B124" t="s">
-        <v>579</v>
       </c>
     </row>
   </sheetData>
@@ -4400,939 +4394,939 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72059C24-7899-4FED-A50B-A4ED81E57F87}">
   <dimension ref="A1:B116"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>256</v>
+        <v>196</v>
       </c>
       <c r="B1" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="B2" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="B3" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>267</v>
+        <v>215</v>
       </c>
       <c r="B4" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="B5" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>257</v>
+        <v>197</v>
       </c>
       <c r="B6" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>282</v>
+      </c>
+      <c r="B7" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>212</v>
+      </c>
+      <c r="B8" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>273</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B9" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>275</v>
-      </c>
-      <c r="B8" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>266</v>
-      </c>
-      <c r="B9" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>268</v>
+        <v>199</v>
       </c>
       <c r="B10" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>272</v>
+      </c>
+      <c r="B11" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>213</v>
+      </c>
+      <c r="B12" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>254</v>
+      </c>
+      <c r="B13" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>198</v>
+      </c>
+      <c r="B14" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>258</v>
       </c>
-      <c r="B11" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="B15" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>271</v>
+      </c>
+      <c r="B16" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>214</v>
+      </c>
+      <c r="B17" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>255</v>
       </c>
-      <c r="B12" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>264</v>
-      </c>
-      <c r="B13" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>271</v>
-      </c>
-      <c r="B14" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>253</v>
-      </c>
-      <c r="B15" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>259</v>
-      </c>
-      <c r="B16" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>254</v>
-      </c>
-      <c r="B17" t="s">
+      <c r="B18" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>260</v>
-      </c>
-      <c r="B18" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="B19" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="B20" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>250</v>
+        <v>192</v>
       </c>
       <c r="B21" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>252</v>
+      </c>
+      <c r="B22" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>306</v>
+      </c>
+      <c r="B23" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>250</v>
+      </c>
+      <c r="B24" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>193</v>
+      </c>
+      <c r="B25" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>253</v>
+      </c>
+      <c r="B26" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>307</v>
+      </c>
+      <c r="B27" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>251</v>
+      </c>
+      <c r="B28" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>248</v>
+      </c>
+      <c r="B29" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>195</v>
+      </c>
+      <c r="B30" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>249</v>
+      </c>
+      <c r="B31" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>194</v>
+      </c>
+      <c r="B32" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>244</v>
+      </c>
+      <c r="B33" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>290</v>
+      </c>
+      <c r="B34" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>299</v>
+      </c>
+      <c r="B35" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>291</v>
+      </c>
+      <c r="B36" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>302</v>
+      </c>
+      <c r="B37" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>243</v>
+      </c>
+      <c r="B38" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>269</v>
+      </c>
+      <c r="B39" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>226</v>
+      </c>
+      <c r="B40" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>221</v>
+      </c>
+      <c r="B41" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>242</v>
+      </c>
+      <c r="B42" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>268</v>
+      </c>
+      <c r="B43" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>225</v>
+      </c>
+      <c r="B44" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>241</v>
+      </c>
+      <c r="B45" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>222</v>
+      </c>
+      <c r="B46" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>300</v>
+      </c>
+      <c r="B47" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>296</v>
+      </c>
+      <c r="B48" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>223</v>
+      </c>
+      <c r="B49" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>279</v>
+      </c>
+      <c r="B50" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>301</v>
+      </c>
+      <c r="B51" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>288</v>
+      </c>
+      <c r="B52" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>280</v>
+      </c>
+      <c r="B53" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>292</v>
+      </c>
+      <c r="B54" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>219</v>
+      </c>
+      <c r="B55" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>294</v>
+      </c>
+      <c r="B56" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>220</v>
+      </c>
+      <c r="B57" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>295</v>
+      </c>
+      <c r="B58" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>211</v>
+      </c>
+      <c r="B59" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>200</v>
+      </c>
+      <c r="B60" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>224</v>
+      </c>
+      <c r="B61" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>210</v>
+      </c>
+      <c r="B62" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>259</v>
+      </c>
+      <c r="B63" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>298</v>
+      </c>
+      <c r="B64" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>277</v>
+      </c>
+      <c r="B65" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>293</v>
+      </c>
+      <c r="B66" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>267</v>
+      </c>
+      <c r="B67" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>231</v>
+      </c>
+      <c r="B68" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>216</v>
+      </c>
+      <c r="B69" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>263</v>
+      </c>
+      <c r="B70" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>297</v>
+      </c>
+      <c r="B71" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>278</v>
+      </c>
+      <c r="B72" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>233</v>
+      </c>
+      <c r="B73" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>266</v>
+      </c>
+      <c r="B74" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>235</v>
+      </c>
+      <c r="B75" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>217</v>
+      </c>
+      <c r="B76" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
         <v>265</v>
       </c>
-      <c r="B22" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>251</v>
-      </c>
-      <c r="B23" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>263</v>
-      </c>
-      <c r="B24" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>248</v>
-      </c>
-      <c r="B25" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="B77" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>289</v>
+      </c>
+      <c r="B78" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>227</v>
+      </c>
+      <c r="B79" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>232</v>
+      </c>
+      <c r="B80" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>264</v>
+      </c>
+      <c r="B81" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>201</v>
+      </c>
+      <c r="B82" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>237</v>
+      </c>
+      <c r="B83" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>218</v>
+      </c>
+      <c r="B84" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>261</v>
+      </c>
+      <c r="B85" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>305</v>
+      </c>
+      <c r="B86" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>247</v>
+      </c>
+      <c r="B87" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>236</v>
+      </c>
+      <c r="B88" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>260</v>
+      </c>
+      <c r="B89" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>204</v>
+      </c>
+      <c r="B90" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>238</v>
+      </c>
+      <c r="B91" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>202</v>
+      </c>
+      <c r="B92" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
         <v>262</v>
       </c>
-      <c r="B26" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>249</v>
-      </c>
-      <c r="B27" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>261</v>
-      </c>
-      <c r="B28" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>213</v>
-      </c>
-      <c r="B29" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>214</v>
-      </c>
-      <c r="B30" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>212</v>
-      </c>
-      <c r="B31" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>199</v>
-      </c>
-      <c r="B32" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>215</v>
-      </c>
-      <c r="B33" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+      <c r="B93" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>303</v>
+      </c>
+      <c r="B94" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>246</v>
+      </c>
+      <c r="B95" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>276</v>
+      </c>
+      <c r="B96" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>203</v>
+      </c>
+      <c r="B97" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>239</v>
+      </c>
+      <c r="B98" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>230</v>
+      </c>
+      <c r="B99" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>209</v>
+      </c>
+      <c r="B100" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>304</v>
+      </c>
+      <c r="B101" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>245</v>
+      </c>
+      <c r="B102" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>275</v>
+      </c>
+      <c r="B103" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>207</v>
+      </c>
+      <c r="B104" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>240</v>
+      </c>
+      <c r="B105" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>234</v>
+      </c>
+      <c r="B106" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>228</v>
+      </c>
+      <c r="B107" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>208</v>
+      </c>
+      <c r="B108" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>286</v>
+      </c>
+      <c r="B109" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>229</v>
+      </c>
+      <c r="B110" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>274</v>
+      </c>
+      <c r="B111" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
         <v>205</v>
       </c>
-      <c r="B34" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>198</v>
-      </c>
-      <c r="B35" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>204</v>
-      </c>
-      <c r="B36" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>218</v>
-      </c>
-      <c r="B37" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>207</v>
-      </c>
-      <c r="B38" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>210</v>
-      </c>
-      <c r="B39" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>203</v>
-      </c>
-      <c r="B40" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>217</v>
-      </c>
-      <c r="B41" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>209</v>
-      </c>
-      <c r="B42" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>211</v>
-      </c>
-      <c r="B43" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>201</v>
-      </c>
-      <c r="B44" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>216</v>
-      </c>
-      <c r="B45" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>208</v>
-      </c>
-      <c r="B46" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>200</v>
-      </c>
-      <c r="B47" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>194</v>
-      </c>
-      <c r="B48" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>196</v>
-      </c>
-      <c r="B49" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>202</v>
-      </c>
-      <c r="B50" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>197</v>
-      </c>
-      <c r="B51" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+      <c r="B112" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
         <v>206</v>
       </c>
-      <c r="B52" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>304</v>
-      </c>
-      <c r="B53" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>300</v>
-      </c>
-      <c r="B54" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>220</v>
-      </c>
-      <c r="B55" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>242</v>
-      </c>
-      <c r="B56" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>303</v>
-      </c>
-      <c r="B57" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>299</v>
-      </c>
-      <c r="B58" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>219</v>
-      </c>
-      <c r="B59" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>243</v>
-      </c>
-      <c r="B60" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>305</v>
-      </c>
-      <c r="B61" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>302</v>
-      </c>
-      <c r="B62" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>231</v>
-      </c>
-      <c r="B63" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>241</v>
-      </c>
-      <c r="B64" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>278</v>
-      </c>
-      <c r="B65" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>229</v>
-      </c>
-      <c r="B66" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>236</v>
-      </c>
-      <c r="B67" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>292</v>
-      </c>
-      <c r="B68" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>281</v>
-      </c>
-      <c r="B69" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>301</v>
-      </c>
-      <c r="B70" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>235</v>
-      </c>
-      <c r="B71" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>244</v>
-      </c>
-      <c r="B72" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>277</v>
-      </c>
-      <c r="B73" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>228</v>
-      </c>
-      <c r="B74" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>195</v>
-      </c>
-      <c r="B75" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>294</v>
-      </c>
-      <c r="B76" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>282</v>
-      </c>
-      <c r="B77" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>286</v>
-      </c>
-      <c r="B78" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>237</v>
-      </c>
-      <c r="B79" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>247</v>
-      </c>
-      <c r="B80" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>280</v>
-      </c>
-      <c r="B81" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>227</v>
-      </c>
-      <c r="B82" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>192</v>
-      </c>
-      <c r="B83" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>296</v>
-      </c>
-      <c r="B84" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>284</v>
-      </c>
-      <c r="B85" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
+      <c r="B113" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>256</v>
+      </c>
+      <c r="B114" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
         <v>287</v>
       </c>
-      <c r="B86" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>238</v>
-      </c>
-      <c r="B87" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>246</v>
-      </c>
-      <c r="B88" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>193</v>
-      </c>
-      <c r="B89" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>279</v>
-      </c>
-      <c r="B90" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>225</v>
-      </c>
-      <c r="B91" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>298</v>
-      </c>
-      <c r="B92" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>283</v>
-      </c>
-      <c r="B93" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>239</v>
-      </c>
-      <c r="B94" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>245</v>
-      </c>
-      <c r="B95" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>288</v>
-      </c>
-      <c r="B96" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>240</v>
-      </c>
-      <c r="B97" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>222</v>
-      </c>
-      <c r="B98" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>306</v>
-      </c>
-      <c r="B99" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>297</v>
-      </c>
-      <c r="B100" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
+      <c r="B115" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
         <v>285</v>
       </c>
-      <c r="B101" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
-        <v>234</v>
-      </c>
-      <c r="B102" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
-        <v>223</v>
-      </c>
-      <c r="B103" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>291</v>
-      </c>
-      <c r="B104" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>232</v>
-      </c>
-      <c r="B105" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
-        <v>221</v>
-      </c>
-      <c r="B106" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
-        <v>307</v>
-      </c>
-      <c r="B107" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
-        <v>295</v>
-      </c>
-      <c r="B108" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
-        <v>289</v>
-      </c>
-      <c r="B109" t="s">
+      <c r="B116" t="s">
         <v>416</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
-        <v>230</v>
-      </c>
-      <c r="B110" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
-        <v>224</v>
-      </c>
-      <c r="B111" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
-        <v>290</v>
-      </c>
-      <c r="B112" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
-        <v>233</v>
-      </c>
-      <c r="B113" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
-        <v>226</v>
-      </c>
-      <c r="B114" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
-        <v>272</v>
-      </c>
-      <c r="B115" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
-        <v>293</v>
-      </c>
-      <c r="B116" t="s">
-        <v>423</v>
       </c>
     </row>
   </sheetData>
